--- a/EstablecimientoSalud/excels/AYACUCHO-HUANTA-HUANTA.xlsx
+++ b/EstablecimientoSalud/excels/AYACUCHO-HUANTA-HUANTA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -741,12 +741,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>33502</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50401</t>
+          <t>50411</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,27 +761,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>PUCACOLPA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-12.93884524</t>
+          <t>-12.34923667</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-74.25052065</t>
+          <t>-74.55829167</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>consultorio dental odontofamily</t>
+          <t>PUESTO DE SALUD PALOMA ALEGRE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Jr..tarapaca NUMERO 473 PISO 1 DEPARTAMENTO 1 INTERIOR 1 MANZANA T LOTE 9 URBANIZACION cercado de huanta DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE PALOMA ALEGRE DISTRITO PUCACOLPA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -803,12 +803,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50411</t>
+          <t>50401</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -823,32 +823,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PUCACOLPA</t>
+          <t>HUANTA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-12.34923667</t>
+          <t>-12.93698</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-74.55829167</t>
+          <t>-74.22884</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD PALOMA ALEGRE</t>
+          <t>PUESTO DE SALUD HUANCAYOCC</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE PALOMA ALEGRE DISTRITO PUCACOLPA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE HUANCAYOCC DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-12.93698</t>
+          <t>-12.94185667</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-74.22884</t>
+          <t>-74.26875167</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD HUANCAYOCC</t>
+          <t>PUESTO DE SALUD QUINRAPA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE HUANCAYOCC DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE QUINRAPA DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -927,12 +927,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50401</t>
+          <t>50404</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -947,27 +947,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>IGUAIN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-12.94185667</t>
+          <t>-12.981775</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-74.26875167</t>
+          <t>-74.26951333</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD QUINRAPA</t>
+          <t>PUESTO DE SALUD CHIHUA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE QUINRAPA DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE CHIHUA DISTRITO IGUAIN PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -989,12 +989,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>50404</t>
+          <t>50406</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1009,32 +1009,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IGUAIN</t>
+          <t>SANTILLANA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-12.981775</t>
+          <t>-12.76943</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-74.26951333</t>
+          <t>-74.25808167</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD CHIHUA</t>
+          <t>CENTRO DE SALUD SAN JOSE DE SECCE</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE CHIHUA DISTRITO IGUAIN PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA DE SAN JOSE DE SECCE NUMERO S/N DISTRITO SANTILLANA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1051,12 +1051,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>50406</t>
+          <t>50410</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,32 +1071,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SANTILLANA</t>
+          <t>UCHURACCAY</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-12.76943</t>
+          <t>-12.73218442</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-74.25808167</t>
+          <t>-74.12686077</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD SAN JOSE DE SECCE</t>
+          <t>PUESTO DE SALUD CARHUAHURAN</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PLAZA DE SAN JOSE DE SECCE NUMERO S/N DISTRITO SANTILLANA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE CARHUAHURAN DISTRITO UCHURACCAY PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1113,12 +1113,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50410</t>
+          <t>50408</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1133,32 +1133,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UCHURACCAY</t>
+          <t>LLOCHEGUA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-12.73218442</t>
+          <t>-12.45005667</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-74.12686077</t>
+          <t>-73.965545</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD CARHUAHURAN</t>
+          <t>PUESTO DE SALUD VILLA MEJORADA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE CARHUAHURAN DISTRITO UCHURACCAY PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL VILLA MEJORADA DISTRITO LLOCHEGUA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50408</t>
+          <t>50403</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LLOCHEGUA</t>
+          <t>HUAMANGUILLA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-12.45005667</t>
+          <t>-13.02510167</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-73.965545</t>
+          <t>-74.15692167</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD VILLA MEJORADA</t>
+          <t>PUESTO DE SALUD QUITURARA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL VILLA MEJORADA DISTRITO LLOCHEGUA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE QUITURARA DISTRITO HUAMANGUILLA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1237,12 +1237,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>50403</t>
+          <t>50405</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1257,27 +1257,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HUAMANGUILLA</t>
+          <t>LURICOCHA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-13.02510167</t>
+          <t>-12.91814667</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-74.15692167</t>
+          <t>-74.29727833</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD QUITURARA</t>
+          <t>PUESTO DE SALUD AZANGARO</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE QUITURARA DISTRITO HUAMANGUILLA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE AZANGARO DISTRITO LURICOCHA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1299,12 +1299,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50405</t>
+          <t>50402</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1319,32 +1319,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LURICOCHA</t>
+          <t>AYAHUANCO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-12.91814667</t>
+          <t>-12.59448371</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-74.29727833</t>
+          <t>-74.33137806</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD AZANGARO</t>
+          <t>CENTRO DE SALUD VIRACOCHAN</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE AZANGARO DISTRITO LURICOCHA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PRINCIPAL DE VIRACOCHAN NUMERO S/N DISTRITO AYAHUANCO PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1361,12 +1361,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50402</t>
+          <t>50411</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1381,32 +1381,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AYAHUANCO</t>
+          <t>PUCACOLPA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-12.59448371</t>
+          <t>-12.36005439</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-74.33137806</t>
+          <t>-74.52296092</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD VIRACOCHAN</t>
+          <t>PUESTO SALUD SACHABAMBA HUANTA</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PLAZA PRINCIPAL DE VIRACOCHAN NUMERO S/N DISTRITO AYAHUANCO PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE SACHABAMBA DISTRITO PUCACOLPA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1423,12 +1423,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>50411</t>
+          <t>50403</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1443,32 +1443,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PUCACOLPA</t>
+          <t>HUAMANGUILLA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-12.36005439</t>
+          <t>-13.01059167</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-74.52296092</t>
+          <t>-74.17549167</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>PUESTO SALUD SACHABAMBA HUANTA</t>
+          <t>CENTRO DE SALUD HUAMANGUILLA</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE SACHABAMBA DISTRITO PUCACOLPA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>AVENIDA AV.AYACUCHO S/N NUMERO S/N DISTRITO HUAMANGUILLA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1485,12 +1485,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>50403</t>
+          <t>50407</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1505,32 +1505,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HUAMANGUILLA</t>
+          <t>SIVIA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-13.01059167</t>
+          <t>-12.59179</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-74.17549167</t>
+          <t>-73.8554</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD HUAMANGUILLA</t>
+          <t>PUESTO DE SALUD CCACCAS</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AVENIDA AV.AYACUCHO S/N NUMERO S/N DISTRITO HUAMANGUILLA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE CCACCAS DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>50407</t>
+          <t>50408</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1567,27 +1567,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SIVIA</t>
+          <t>LLOCHEGUA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-12.59179</t>
+          <t>-12.43442</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-73.8554</t>
+          <t>-73.9806112</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD CCACCAS</t>
+          <t>PUESTO DE SALUD AREQUIPA</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE CCACCAS DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DEL C.P. DE AREQUIPA DISTRITO LLOCHEGUA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>36323</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>50408</t>
+          <t>50412</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1629,27 +1629,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LLOCHEGUA</t>
+          <t>CHACA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-12.43442</t>
+          <t>-12.78203828</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-73.9806112</t>
+          <t>-74.16616715</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD AREQUIPA</t>
+          <t>PUESTO DE SALUD  PURUS</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DEL C.P. DE AREQUIPA DISTRITO LLOCHEGUA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>TORONGANA NUMERO S/N DISTRITO CHACA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>34045</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>50401</t>
+          <t>50407</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1691,27 +1691,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>SIVIA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-12.9384113</t>
+          <t>-12.51569</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-74.2502122</t>
+          <t>-73.88953333</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CONSULTORIO DENTAL SABINO</t>
+          <t>PUESTO DE SALUD CHUVIVANA</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Tarapaca NUMERO 415 PISO 1 DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE CHUVIVANA DISTRITO SIVIA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1733,12 +1733,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>36323</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>50412</t>
+          <t>50403</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1753,27 +1753,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CHACA</t>
+          <t>HUAMANGUILLA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-12.78203828</t>
+          <t>-13.01266667</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-74.16616715</t>
+          <t>-74.20271333</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD  PURUS</t>
+          <t>PUESTO DE SALUD ICHUPATA</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TORONGANA NUMERO S/N DISTRITO CHACA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE ICHUPATA DISTRITO HUAMANGUILLA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1795,12 +1795,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>50407</t>
+          <t>50406</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1815,27 +1815,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SIVIA</t>
+          <t>SANTILLANA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-12.51569</t>
+          <t>-12.69176648</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-73.88953333</t>
+          <t>-74.23745841</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD CHUVIVANA</t>
+          <t>PUESTO DE SALUD MARQARAQAY</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE CHUVIVANA DISTRITO SIVIA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE MAQARAQAY DISTRITO SANTILLANA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1857,12 +1857,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>50403</t>
+          <t>50407</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1877,27 +1877,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HUAMANGUILLA</t>
+          <t>SIVIA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-13.01266667</t>
+          <t>-12.601825</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-74.20271333</t>
+          <t>-73.849268</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD ICHUPATA</t>
+          <t>PUESTO DE SALUD MATUCANA</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE ICHUPATA DISTRITO HUAMANGUILLA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>OTROS LTE 6 MZ B. MATUCANA DISTRITO SIVIA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>50406</t>
+          <t>50412</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1939,32 +1939,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SANTILLANA</t>
+          <t>CHACA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-12.69176648</t>
+          <t>-12.78415747</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-74.23745841</t>
+          <t>-74.20562204</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD MARQARAQAY</t>
+          <t>PUESTO DE SALUD CHACA</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE MAQARAQAY DISTRITO SANTILLANA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE CHACA DISTRITO CHACA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1981,12 +1981,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>50407</t>
+          <t>50408</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2001,27 +2001,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SIVIA</t>
+          <t>LLOCHEGUA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-12.601825</t>
+          <t>-12.45725833</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-73.849268</t>
+          <t>-74.017865</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD MATUCANA</t>
+          <t>PUESTO DE SALUD CHONGOS CARMEN PAMPA</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>OTROS LTE 6 MZ B. MATUCANA DISTRITO SIVIA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DISTRITO LLOCHEGUA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2043,12 +2043,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>50412</t>
+          <t>50413</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2063,32 +2063,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CHACA</t>
+          <t>PUTIS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-12.78415747</t>
+          <t>-12.62557739</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-74.20562204</t>
+          <t>-74.1955548</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD CHACA</t>
+          <t>PUESTO DE SALUD VISCATAN</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE CHACA DISTRITO CHACA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE NUEVO RODEO DISTRITO SANTILLANA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2105,12 +2105,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>50408</t>
+          <t>50409</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2125,32 +2125,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LLOCHEGUA</t>
+          <t>CANAYRE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-12.45725833</t>
+          <t>-12.281745</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-74.017865</t>
+          <t>-74.02379833</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD CHONGOS CARMEN PAMPA</t>
+          <t>PUESTO DE SALUD CANAYRE</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DISTRITO LLOCHEGUA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>OTROS LOTE: 05 MANZANA: P CANAYRE DISTRITO CANAYRE PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2167,12 +2167,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>50413</t>
+          <t>50411</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2187,32 +2187,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PUTIS</t>
+          <t>PUCACOLPA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-12.62557739</t>
+          <t>-12.42020401</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-74.1955548</t>
+          <t>-74.48951756</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD VISCATAN</t>
+          <t>PUESTO DE SALUD HUALLHUA</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE NUEVO RODEO DISTRITO SANTILLANA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE HUALLHUA DISTRITO PUCACOLPA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2229,12 +2229,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>50409</t>
+          <t>50404</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2249,32 +2249,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CANAYRE</t>
+          <t>IGUAIN</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-12.281745</t>
+          <t>-13.01206167</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-74.02379833</t>
+          <t>-74.24662833</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD CANAYRE</t>
+          <t>PUESTO DE SALUD  ALLCOHUILLCA</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>OTROS LOTE: 05 MANZANA: P CANAYRE DISTRITO CANAYRE PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE ALLCOHUILLCA DISTRITO IGUAIN PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2291,12 +2291,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>50411</t>
+          <t>50407</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2311,32 +2311,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PUCACOLPA</t>
+          <t>SIVIA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-12.42020401</t>
+          <t>-12.72743167</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-74.48951756</t>
+          <t>-73.94693</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD HUALLHUA</t>
+          <t>PUESTO DE SALUD TUTUMBARU</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE HUALLHUA DISTRITO PUCACOLPA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL TUTUMBARU DISTRITO SIVIA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2353,12 +2353,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>50404</t>
+          <t>50411</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2373,27 +2373,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IGUAIN</t>
+          <t>PUCACOLPA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-13.01206167</t>
+          <t>-12.35005833</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-74.24662833</t>
+          <t>-74.43818833</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD  ALLCOHUILLCA</t>
+          <t>PUESTO DE SALUD PUCACOLPA</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE ALLCOHUILLCA DISTRITO IGUAIN PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE PUCACOLPA DISTRITO PUCACOLPA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2415,12 +2415,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>25161</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>50407</t>
+          <t>50405</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2435,27 +2435,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SIVIA</t>
+          <t>LURICOCHA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-12.72743167</t>
+          <t>-12.89560364</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-73.94693</t>
+          <t>-74.28349203</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD TUTUMBARU</t>
+          <t>PUESTO DE SALUD AICAS</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL TUTUMBARU DISTRITO SIVIA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>AVENIDA REPUBLICA DE AICAS NUMERO S/N MANZANA Y DISTRITO LURICOCHA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2477,12 +2477,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>27666</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>50411</t>
+          <t>50401</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2497,32 +2497,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PUCACOLPA</t>
+          <t>HUANTA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-12.35005833</t>
+          <t>-12.9319864</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-74.43818833</t>
+          <t>-74.2554476</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD PUCACOLPA</t>
+          <t>PUESTO DE SALUD JERUSALEN</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE PUCACOLPA DISTRITO PUCACOLPA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>LOS ANDES NUMERO 121 PISO 2 DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2539,12 +2539,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>25161</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>50405</t>
+          <t>50402</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2559,27 +2559,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LURICOCHA</t>
+          <t>AYAHUANCO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-12.89560364</t>
+          <t>-12.58067775</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-74.28349203</t>
+          <t>-74.36176917</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD AICAS</t>
+          <t>PUESTO DE SALUD QOCHACC</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AVENIDA REPUBLICA DE AICAS NUMERO S/N MANZANA Y DISTRITO LURICOCHA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE QOCHACC DISTRITO AYAHUANCO PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>27666</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>50401</t>
+          <t>50407</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2621,32 +2621,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>SIVIA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-12.9319864</t>
+          <t>-12.48872</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-74.2554476</t>
+          <t>-73.94510833</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD JERUSALEN</t>
+          <t>PUESTO DE SALUD SAN GERARDO</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>LOS ANDES NUMERO 121 PISO 2 DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL SAN GERARDO DISTRITO SIVIA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2663,12 +2663,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>34687</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>50408</t>
+          <t>50407</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2683,27 +2683,27 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LLOCHEGUA</t>
+          <t>SIVIA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-12.4092319</t>
+          <t>-12.57937167</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-73.90606266</t>
+          <t>-73.85807333</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO PROSAMAS L&amp;M</t>
+          <t>CENTRO DE SALUD TRIBOLINE</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CHOYMACOTA NUMERO S/N DISTRITO LLOCHEGUA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL TRIBOLINE DISTRITO SIVIA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2725,12 +2725,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>33788</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>50401</t>
+          <t>50404</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2745,32 +2745,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>IGUAIN</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-12.9304387</t>
+          <t>-12.994925</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-74.2556384</t>
+          <t>-74.20873167</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO HUANTA</t>
+          <t>PUESTO DE SALUD IGUAIN</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>RAZUHUILCA NUMERO 290 DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE IGUAIN DISTRITO IGUAIN PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2787,7 +2787,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2812,22 +2812,22 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-12.58067775</t>
+          <t>-12.51962467</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-74.36176917</t>
+          <t>-74.3741411</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD QOCHACC</t>
+          <t>PUESTO DE SALUD PAMPA CCORIS</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE QOCHACC DISTRITO AYAHUANCO PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE PAMPA CORIS DISTRITO AYAHUANCO PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2849,12 +2849,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>50407</t>
+          <t>50401</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2869,27 +2869,27 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SIVIA</t>
+          <t>HUANTA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-12.48872</t>
+          <t>-12.87773167</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-73.94510833</t>
+          <t>-74.22252333</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD SAN GERARDO</t>
+          <t>PUESTO DE SALUD SAN ANTONIO DE CULLUCHACA</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL SAN GERARDO DISTRITO SIVIA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE CULLUCHACA DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2911,12 +2911,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>50407</t>
+          <t>50411</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SIVIA</t>
+          <t>PUCACOLPA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-12.57937167</t>
+          <t>-12.42713634</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-73.85807333</t>
+          <t>-74.38401418</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD TRIBOLINE</t>
+          <t>PUESTO DE SALUD HUARCATAN</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL TRIBOLINE DISTRITO SIVIA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE HUARCATAN DISTRITO PUCACOLPA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2973,12 +2973,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>50404</t>
+          <t>50401</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2993,32 +2993,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IGUAIN</t>
+          <t>HUANTA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-12.994925</t>
+          <t>-12.93720881</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-74.20873167</t>
+          <t>-74.24481828</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD IGUAIN</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO  BELLA ESMERALDAÂ´Â´ - HUANTA</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE IGUAIN DISTRITO IGUAIN PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>Â´MONTONEROS NUMERO 140 PISO 1 DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3035,12 +3035,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>11437</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>50402</t>
+          <t>50401</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3055,32 +3055,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AYAHUANCO</t>
+          <t>HUANTA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-12.51962467</t>
+          <t>-12.94020449</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-74.3741411</t>
+          <t>-74.24704987</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD PAMPA CCORIS</t>
+          <t>POSTA MEDICA PNP HUANTA</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE PAMPA CORIS DISTRITO AYAHUANCO PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>JR. AYACUCHO Nº 271 DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3097,12 +3097,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>50401</t>
+          <t>50402</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3117,27 +3117,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>AYAHUANCO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-12.87773167</t>
+          <t>-12.57836708</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-74.22252333</t>
+          <t>-74.34692901</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD SAN ANTONIO DE CULLUCHACA</t>
+          <t>PUESTO DE SALUD MAYHUAVILCA</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE CULLUCHACA DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE MAYHUAVILCA DISTRITO AYAHUANCO PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3159,12 +3159,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>50411</t>
+          <t>50408</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3179,32 +3179,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PUCACOLPA</t>
+          <t>LLOCHEGUA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-12.42713634</t>
+          <t>-12.41615833</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-74.38401418</t>
+          <t>-73.90994667</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD HUARCATAN</t>
+          <t>CENTRO DE SALUD LLOCHEGUA</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE HUARCATAN DISTRITO PUCACOLPA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>OTROS PERIAVENTE-ZONA CHOYMACOTA NUMERO S/N DISTRITO LLOCHEGUA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3221,12 +3221,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>50401</t>
+          <t>50410</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3241,32 +3241,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>UCHURACCAY</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-12.93720881</t>
+          <t>-12.82676187</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-74.24481828</t>
+          <t>-74.11111642</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO  BELLA ESMERALDAÂ´Â´ - HUANTA</t>
+          <t>PUESTO DE SALUD UCHURACCAY</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Â´MONTONEROS NUMERO 140 PISO 1 DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE UCHURACCAY DISTRITO UCHURACCAY PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3283,12 +3283,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>50401</t>
+          <t>50410</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3303,32 +3303,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>UCHURACCAY</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-12.94020449</t>
+          <t>-12.7590439</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-74.24704987</t>
+          <t>-74.14695235</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>POSTA MEDICA PNP HUANTA</t>
+          <t>PUESTO DE SALUD HUAYNACANCHA</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>JR. AYACUCHO Nº 271 DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE HUAYNACANCHA DISTRITO UCHURACCAY PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3345,12 +3345,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>50402</t>
+          <t>50408</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3365,27 +3365,27 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AYAHUANCO</t>
+          <t>LLOCHEGUA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-12.57836708</t>
+          <t>-12.45283667</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-74.34692901</t>
+          <t>-73.94549667</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD MAYHUAVILCA</t>
+          <t>PUESTO DE SALUD YARURI</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE MAYHUAVILCA DISTRITO AYAHUANCO PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL YARURI DISTRITO LLOCHEGUA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3407,12 +3407,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>24947</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>50408</t>
+          <t>50411</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3427,32 +3427,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>LLOCHEGUA</t>
+          <t>PUCACOLPA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-12.41615833</t>
+          <t>-12.4207615</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-73.90994667</t>
+          <t>-74.46174658</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD LLOCHEGUA</t>
+          <t>PUESTO DE SALUD CHACHASPATA</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>OTROS PERIAVENTE-ZONA CHOYMACOTA NUMERO S/N DISTRITO LLOCHEGUA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>CARRETERA CENTRO POBLADO CHACHASPATA NUMERO S/N DISTRITO PUCACOLPA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>I-4</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3469,12 +3469,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>50410</t>
+          <t>50408</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3489,32 +3489,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UCHURACCAY</t>
+          <t>LLOCHEGUA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-12.82676187</t>
+          <t>-12.41505833</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-74.11111642</t>
+          <t>-74.00073667</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD UCHURACCAY</t>
+          <t>PUESTO DE SALUD GLORIA SOL NACIENTE</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE UCHURACCAY DISTRITO UCHURACCAY PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>CALLE CALLE PRINCIPAL GLORIA SOL NACIENTE DISTRITO LLOCHEGUA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3531,12 +3531,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>50410</t>
+          <t>50407</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3551,27 +3551,27 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>UCHURACCAY</t>
+          <t>SIVIA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-12.7590439</t>
+          <t>-12.50626333</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-74.14695235</t>
+          <t>-73.91551333</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD HUAYNACANCHA</t>
+          <t>PUESTO DE SALUD GUAYAQUIL</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL DE HUAYNACANCHA DISTRITO UCHURACCAY PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL GUAYAQUIL DISTRITO SIVIA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3593,7 +3593,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3618,22 +3618,22 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-12.45283667</t>
+          <t>-12.360195</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-73.94549667</t>
+          <t>-73.95814833</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD YARURI</t>
+          <t>PUESTO DE SALUD MAYAPO</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL YARURI DISTRITO LLOCHEGUA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>CALLE CALLE PRINCIPAL MAYAPO DISTRITO CANAYRE PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3655,12 +3655,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>24947</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>50411</t>
+          <t>50408</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3675,27 +3675,27 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PUCACOLPA</t>
+          <t>LLOCHEGUA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-12.4207615</t>
+          <t>-12.446985</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-74.46174658</t>
+          <t>-73.99622167</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD CHACHASPATA</t>
+          <t>PUESTO DE SALUD CORAZONPATA</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CARRETERA CENTRO POBLADO CHACHASPATA NUMERO S/N DISTRITO PUCACOLPA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL CORAZON PATA DISTRITO LLOCHEGUA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3717,12 +3717,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>50408</t>
+          <t>50405</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3737,32 +3737,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>LLOCHEGUA</t>
+          <t>LURICOCHA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-12.41505833</t>
+          <t>-12.90005333</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-74.00073667</t>
+          <t>-74.272135</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD GLORIA SOL NACIENTE</t>
+          <t>CENTRO DE SALUD LURICOCHA</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CALLE CALLE PRINCIPAL GLORIA SOL NACIENTE DISTRITO LLOCHEGUA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>JR. DELFIN LUDEAA S/N NUMERO S/N DISTRITO LURICOCHA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3779,12 +3779,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>50407</t>
+          <t>50402</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3799,27 +3799,27 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SIVIA</t>
+          <t>AYAHUANCO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-12.50626333</t>
+          <t>-12.63289104</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-73.91551333</t>
+          <t>-74.29150336</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD GUAYAQUIL</t>
+          <t>PUESTO DE SALUD AYAHUANCO</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL GUAYAQUIL DISTRITO SIVIA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE AYAHUANCO DISTRITO AYAHUANCO PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3841,12 +3841,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>31379</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>50401</t>
+          <t>50410</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3861,32 +3861,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HUANTA</t>
+          <t>UCHURACCAY</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-12.94379688</t>
+          <t>-12.75855763</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-74.24798069</t>
+          <t>-74.07051655</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO  THANIY</t>
+          <t>PUESTO DE SALUD PAMPALCA</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>VICTOR FAJARDO NUMERO 281 PISO 1 DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL PAMPALCA DISTRITO UCHURACCAY PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3903,7 +3903,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>36770</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3928,32 +3928,32 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-12.93604515</t>
+          <t>-12.95522667</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-74.25203539</t>
+          <t>-74.25181333</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO VIDA DIOSPI SUYANA</t>
+          <t>PUESTO DE SALUD MAYNAY</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>AVENIDA MARISCAL CASTILLA NUMERO 702 DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PLAZA PLAZA PRINCIPAL DE MAYNAY DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3965,12 +3965,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>36468</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>50408</t>
+          <t>50401</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3985,27 +3985,27 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>LLOCHEGUA</t>
+          <t>HUANTA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-12.360195</t>
+          <t>-12.9468779</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-73.95814833</t>
+          <t>-74.24062259</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD MAYAPO</t>
+          <t>PUESTO DE SALUD  ACCOSCCA</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CALLE CALLE PRINCIPAL MAYAPO DISTRITO CANAYRE PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>PASAJE SAN MARTIN-BARRIO ACCOSCCA NUMERO S/N DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4027,12 +4027,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>29745</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>50408</t>
+          <t>50401</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4047,32 +4047,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>LLOCHEGUA</t>
+          <t>HUANTA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-12.446985</t>
+          <t>-12.93032834</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-73.99622167</t>
+          <t>-74.25095249</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD CORAZONPATA</t>
+          <t>ENFERMERIA LOS CABITOS NÂ° 51</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>PLAZA PLAZA PRINCIPAL CORAZON PATA DISTRITO LLOCHEGUA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>circunvalacion NUMERO S/N DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4089,12 +4089,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>11446</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>50405</t>
+          <t>50401</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4109,27 +4109,27 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>LURICOCHA</t>
+          <t>HUANTA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-12.90005333</t>
+          <t>-12.93887256</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-74.272135</t>
+          <t>-74.24044</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD LURICOCHA</t>
+          <t>HUANTA</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>JR. DELFIN LUDEAA S/N NUMERO S/N DISTRITO LURICOCHA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
+          <t>AVENIDA AV. CIRCUNVALACION S/N NUMERO S/N DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4143,440 +4143,6 @@
         </is>
       </c>
       <c r="L60" t="inlineStr">
-        <is>
-          <t>050401</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>3671</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>50402</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AYAHUANCO</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-12.63289104</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>-74.29150336</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>PUESTO DE SALUD AYAHUANCO</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>PLAZA PLAZA PRINCIPAL DE AYAHUANCO DISTRITO AYAHUANCO PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>050401</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>6652</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>50410</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>UCHURACCAY</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-12.75855763</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-74.07051655</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>PUESTO DE SALUD PAMPALCA</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>PLAZA PLAZA PRINCIPAL PAMPALCA DISTRITO UCHURACCAY PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>050401</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>3659</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>50401</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-12.95522667</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>-74.25181333</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>PUESTO DE SALUD MAYNAY</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>PLAZA PLAZA PRINCIPAL DE MAYNAY DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>050401</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>31357</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>50401</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-12.9386074</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-74.2497037</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>VELIZ CONSULTORIOÂ´S ODONTOLOGICOS</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Mariscal castilla NUMERO 393 PISO 2 DEPARTAMENTO 6 DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>050401</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>34435</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>50401</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-12.93724018</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>-74.24650002</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>CENTRO MADICO SAN CRISTABAL</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>ARICA NUMERO 499 DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>I-3</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>050401</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>36468</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>50401</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-12.9468779</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>-74.24062259</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>PUESTO DE SALUD  ACCOSCCA</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>PASAJE SAN MARTIN-BARRIO ACCOSCCA NUMERO S/N DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>050401</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>36756</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>50401</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-12.9386109</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>-74.25049113</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>CONSULTORIO DENTAL HUANTA</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>TARAPACA NUMERO 479 PISO 1 DISTRITO HUANTA PROVINCIA HUANTA DEPARTAMENTO AYACUCHO</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>I-1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
         <is>
           <t>050401</t>
         </is>

--- a/EstablecimientoSalud/excels/AYACUCHO-HUANTA-HUANTA.xlsx
+++ b/EstablecimientoSalud/excels/AYACUCHO-HUANTA-HUANTA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>3776</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>50408</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LLOCHEGUA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-12.40054333</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>7304</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>50407</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SIVIA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-12.539309</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>6908</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>50408</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>LLOCHEGUA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-12.43457</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>10366</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>50410</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>UCHURACCAY</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-12.83232922</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>3648</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>50411</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>PUCACOLPA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-12.34923667</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>3658</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>50401</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-12.93698</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>3660</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>50401</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-12.94185667</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>3662</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>50404</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>IGUAIN</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-12.981775</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>3667</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>50406</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>SANTILLANA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-12.76943</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>3656</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>50410</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>UCHURACCAY</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-12.73218442</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>3748</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>50408</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LLOCHEGUA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-12.45005667</t>
@@ -1164,40 +1109,35 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>3651</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>50403</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>HUAMANGUILLA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-13.02510167</t>
@@ -1226,40 +1166,35 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>3664</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50405</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>LURICOCHA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-12.91814667</t>
@@ -1288,40 +1223,35 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>3676</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>50402</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AYAHUANCO</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-12.59448371</t>
@@ -1350,40 +1280,35 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>3649</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>50411</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PUCACOLPA</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-12.36005439</t>
@@ -1412,40 +1337,35 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>3650</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>50403</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>HUAMANGUILLA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-13.01059167</t>
@@ -1474,40 +1394,35 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>3657</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>50407</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>SIVIA</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-12.59179</t>
@@ -1536,40 +1451,35 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>6910</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>50408</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>LLOCHEGUA</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-12.43442</t>
@@ -1598,40 +1508,35 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>36323</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>50412</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>CHACA</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-12.78203828</t>
@@ -1660,40 +1565,35 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>3778</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>50407</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>SIVIA</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-12.51569</t>
@@ -1722,40 +1622,35 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>3652</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>50403</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>HUAMANGUILLA</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-13.01266667</t>
@@ -1784,40 +1679,35 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>10362</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>50406</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>SANTILLANA</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-12.69176648</t>
@@ -1846,40 +1736,35 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>3773</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>50407</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>SIVIA</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-12.601825</t>
@@ -1908,40 +1793,35 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>3669</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>50412</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>CHACA</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-12.78415747</t>
@@ -1970,40 +1850,35 @@
       <c r="K25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>6912</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>50408</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>LLOCHEGUA</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-12.45725833</t>
@@ -2032,40 +1907,35 @@
       <c r="K26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>3665</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>50413</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>PUTIS</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-12.62557739</t>
@@ -2094,40 +1964,35 @@
       <c r="K27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>3771</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>50409</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>CANAYRE</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-12.281745</t>
@@ -2156,40 +2021,35 @@
       <c r="K28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>3647</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>50411</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>PUCACOLPA</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-12.42020401</t>
@@ -2218,40 +2078,35 @@
       <c r="K29" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>3653</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>50404</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>IGUAIN</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-13.01206167</t>
@@ -2280,40 +2135,35 @@
       <c r="K30" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>6911</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>50407</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>SIVIA</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>-12.72743167</t>
@@ -2342,40 +2192,35 @@
       <c r="K31" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>10365</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>50411</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>PUCACOLPA</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-12.35005833</t>
@@ -2404,40 +2249,35 @@
       <c r="K32" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>25161</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>50405</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>LURICOCHA</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>-12.89560364</t>
@@ -2466,40 +2306,35 @@
       <c r="K33" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>27666</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>50401</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>-12.9319864</t>
@@ -2528,40 +2363,35 @@
       <c r="K34" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>3673</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>50402</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AYAHUANCO</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>-12.58067775</t>
@@ -2590,40 +2420,35 @@
       <c r="K35" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>3774</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>50407</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>SIVIA</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>-12.48872</t>
@@ -2652,40 +2477,35 @@
       <c r="K36" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>3775</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>50407</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>SIVIA</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>-12.57937167</t>
@@ -2714,40 +2534,35 @@
       <c r="K37" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>3654</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>50404</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>IGUAIN</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>-12.994925</t>
@@ -2776,40 +2591,35 @@
       <c r="K38" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>3675</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>50402</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AYAHUANCO</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>-12.51962467</t>
@@ -2838,40 +2648,35 @@
       <c r="K39" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>6653</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>50401</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>-12.87773167</t>
@@ -2900,40 +2705,35 @@
       <c r="K40" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>3672</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>50411</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>PUCACOLPA</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>-12.42713634</t>
@@ -2962,40 +2762,35 @@
       <c r="K41" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>26014</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>50401</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>-12.93720881</t>
@@ -3024,40 +2819,35 @@
       <c r="K42" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>11437</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>50401</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>-12.94020449</t>
@@ -3086,40 +2876,35 @@
       <c r="K43" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>3674</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>50402</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AYAHUANCO</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>-12.57836708</t>
@@ -3148,40 +2933,35 @@
       <c r="K44" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>3745</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>50408</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>LLOCHEGUA</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>-12.41615833</t>
@@ -3210,40 +2990,35 @@
       <c r="K45" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>3796</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>50410</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>UCHURACCAY</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>-12.82676187</t>
@@ -3272,40 +3047,35 @@
       <c r="K46" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>10367</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>50410</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>UCHURACCAY</t>
-        </is>
-      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>-12.7590439</t>
@@ -3334,40 +3104,35 @@
       <c r="K47" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>3747</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>50408</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>LLOCHEGUA</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>-12.45283667</t>
@@ -3396,40 +3161,35 @@
       <c r="K48" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>24947</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>50411</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>PUCACOLPA</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>-12.4207615</t>
@@ -3458,40 +3218,35 @@
       <c r="K49" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>6752</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>50408</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>LLOCHEGUA</t>
-        </is>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>-12.41505833</t>
@@ -3520,40 +3275,35 @@
       <c r="K50" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>3777</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>50407</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>SIVIA</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>-12.50626333</t>
@@ -3582,40 +3332,35 @@
       <c r="K51" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>3772</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>50408</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>LLOCHEGUA</t>
-        </is>
-      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>-12.360195</t>
@@ -3644,40 +3389,35 @@
       <c r="K52" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>3746</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>50408</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>LLOCHEGUA</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>-12.446985</t>
@@ -3706,40 +3446,35 @@
       <c r="K53" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>3663</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>50405</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>LURICOCHA</t>
-        </is>
-      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>-12.90005333</t>
@@ -3768,40 +3503,35 @@
       <c r="K54" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>3671</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>50402</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AYAHUANCO</t>
-        </is>
-      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>-12.63289104</t>
@@ -3830,40 +3560,35 @@
       <c r="K55" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>6652</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>50410</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>UCHURACCAY</t>
-        </is>
-      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>-12.75855763</t>
@@ -3892,40 +3617,35 @@
       <c r="K56" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>3659</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>50401</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>-12.95522667</t>
@@ -3954,40 +3674,35 @@
       <c r="K57" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>36468</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>50401</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>-12.9468779</t>
@@ -4016,40 +3731,35 @@
       <c r="K58" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>29745</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>50401</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>-12.93032834</t>
@@ -4078,40 +3788,35 @@
       <c r="K59" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>050401</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>HUANTA</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>11446</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>50401</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>HUANTA</t>
-        </is>
-      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>-12.93887256</t>
@@ -4140,11 +3845,6 @@
       <c r="K60" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>050401</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/AYACUCHO-HUANTA-HUANTA.xlsx
+++ b/EstablecimientoSalud/excels/AYACUCHO-HUANTA-HUANTA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
